--- a/reports/scan/fs_law_firm_fs.xlsx
+++ b/reports/scan/fs_law_firm_fs.xlsx
@@ -532,72 +532,72 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -629,17 +629,17 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -706,22 +706,22 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -776,9 +776,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -791,9 +791,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -868,9 +868,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -945,9 +945,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1007,9 +1007,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1022,9 +1022,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1099,9 +1099,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1176,9 +1176,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1238,9 +1238,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1253,9 +1253,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1330,9 +1330,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1407,9 +1407,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1454,74 +1454,74 @@
           <t>/</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1633,9 +1633,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1710,9 +1710,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2092,37 +2092,37 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2169,37 +2169,37 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">

--- a/reports/scan/fs_law_firm_fs.xlsx
+++ b/reports/scan/fs_law_firm_fs.xlsx
@@ -532,72 +532,72 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -609,62 +609,62 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -699,9 +699,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -719,9 +719,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -729,9 +729,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -739,9 +739,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -776,14 +776,14 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -853,9 +853,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -935,9 +935,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1007,14 +1007,14 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1084,9 +1084,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1166,9 +1166,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1454,74 +1454,74 @@
           <t>/</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1551,16 +1551,16 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1638,9 +1638,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1715,9 +1715,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1782,16 +1782,16 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1859,16 +1859,16 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1936,16 +1936,16 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2018,9 +2018,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2095,9 +2095,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2172,9 +2172,9 @@
           <t>18</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">

--- a/reports/scan/fs_law_firm_fs.xlsx
+++ b/reports/scan/fs_law_firm_fs.xlsx
@@ -629,12 +629,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -734,9 +734,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -811,9 +811,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -935,9 +935,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1042,9 +1042,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1166,9 +1166,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1504,9 +1504,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2018,9 +2018,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2043,9 +2043,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2172,9 +2172,9 @@
           <t>18</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
